--- a/research/traditional_assets/database/data/france/france_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0116</v>
+        <v>-0.0386</v>
       </c>
       <c r="E2">
-        <v>-0.0005600000000000001</v>
+        <v>0.0469</v>
       </c>
       <c r="F2">
-        <v>0.215</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G2">
-        <v>0.05618343084438512</v>
+        <v>0.1070767345525261</v>
       </c>
       <c r="H2">
-        <v>0.05618343084438512</v>
+        <v>0.1070767345525261</v>
       </c>
       <c r="I2">
-        <v>0.06575093684141886</v>
+        <v>0.09264976845993668</v>
       </c>
       <c r="J2">
-        <v>0.05095845956946215</v>
+        <v>0.07515209517429933</v>
       </c>
       <c r="K2">
-        <v>6795.1</v>
+        <v>7742</v>
       </c>
       <c r="L2">
-        <v>0.04713758700728246</v>
+        <v>0.06874719732186067</v>
       </c>
       <c r="M2">
-        <v>6471.5</v>
+        <v>7696</v>
       </c>
       <c r="N2">
-        <v>0.09093540586151515</v>
+        <v>0.1157982798779424</v>
       </c>
       <c r="O2">
-        <v>0.9523774484555046</v>
+        <v>0.9940583828468096</v>
       </c>
       <c r="P2">
-        <v>6170.3</v>
+        <v>4016.3</v>
       </c>
       <c r="Q2">
-        <v>0.08670304176578952</v>
+        <v>0.06043147498359926</v>
       </c>
       <c r="R2">
-        <v>0.9080513899721858</v>
+        <v>0.5187677602686644</v>
       </c>
       <c r="S2">
-        <v>301.1999999999998</v>
+        <v>3679.7</v>
       </c>
       <c r="T2">
-        <v>0.04654253264312753</v>
+        <v>0.4781314968814969</v>
       </c>
       <c r="U2">
-        <v>31761.9</v>
+        <v>25871.8</v>
       </c>
       <c r="V2">
-        <v>0.4463078524967717</v>
+        <v>0.389281436765352</v>
       </c>
       <c r="W2">
-        <v>0.08617886385081321</v>
+        <v>0.09539652028192616</v>
       </c>
       <c r="X2">
-        <v>0.06941631435079323</v>
+        <v>0.1090515518677914</v>
       </c>
       <c r="Y2">
-        <v>0.01676254950001997</v>
+        <v>-0.01365503158586526</v>
       </c>
       <c r="Z2">
-        <v>1.523118113697166</v>
+        <v>1.175668269155483</v>
       </c>
       <c r="AA2">
-        <v>0.07761575281635245</v>
+        <v>0.08835393365697664</v>
       </c>
       <c r="AB2">
-        <v>0.04682024093996177</v>
+        <v>0.07717571187450774</v>
       </c>
       <c r="AC2">
-        <v>0.03079551187639069</v>
+        <v>0.0111782217824689</v>
       </c>
       <c r="AD2">
-        <v>66299.5</v>
+        <v>61725.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>66299.5</v>
+        <v>61725.9</v>
       </c>
       <c r="AG2">
-        <v>34537.6</v>
+        <v>35854.10000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4822995459221012</v>
+        <v>0.4815327378978878</v>
       </c>
       <c r="AI2">
-        <v>0.4109792413625522</v>
+        <v>0.4874800983080403</v>
       </c>
       <c r="AJ2">
-        <v>0.3267403633749119</v>
+        <v>0.3504302909167323</v>
       </c>
       <c r="AK2">
-        <v>0.2665783670593066</v>
+        <v>0.3558698409736518</v>
       </c>
       <c r="AL2">
-        <v>578.6</v>
+        <v>381.6</v>
       </c>
       <c r="AM2">
-        <v>578.6</v>
+        <v>381.6</v>
       </c>
       <c r="AN2">
-        <v>6.325443165989276</v>
+        <v>5.346501979194636</v>
       </c>
       <c r="AO2">
-        <v>16.3814379536813</v>
+        <v>27.34224318658281</v>
       </c>
       <c r="AP2">
-        <v>3.295132329650619</v>
+        <v>3.105568596200986</v>
       </c>
       <c r="AQ2">
-        <v>16.3814379536813</v>
+        <v>27.34224318658281</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0116</v>
+        <v>-0.0386</v>
       </c>
       <c r="E3">
-        <v>-0.0005600000000000001</v>
+        <v>0.0469</v>
       </c>
       <c r="F3">
-        <v>0.215</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G3">
-        <v>0.05618343084438512</v>
+        <v>0.1070767345525261</v>
       </c>
       <c r="H3">
-        <v>0.05618343084438512</v>
+        <v>0.1070767345525261</v>
       </c>
       <c r="I3">
-        <v>0.06575093684141886</v>
+        <v>0.09264976845993668</v>
       </c>
       <c r="J3">
-        <v>0.05095845956946215</v>
+        <v>0.07515209517429933</v>
       </c>
       <c r="K3">
-        <v>6795.1</v>
+        <v>7742</v>
       </c>
       <c r="L3">
-        <v>0.04713758700728246</v>
+        <v>0.06874719732186067</v>
       </c>
       <c r="M3">
-        <v>6471.5</v>
+        <v>7696</v>
       </c>
       <c r="N3">
-        <v>0.09093540586151515</v>
+        <v>0.1157982798779424</v>
       </c>
       <c r="O3">
-        <v>0.9523774484555046</v>
+        <v>0.9940583828468096</v>
       </c>
       <c r="P3">
-        <v>6170.3</v>
+        <v>4016.3</v>
       </c>
       <c r="Q3">
-        <v>0.08670304176578952</v>
+        <v>0.06043147498359926</v>
       </c>
       <c r="R3">
-        <v>0.9080513899721858</v>
+        <v>0.5187677602686644</v>
       </c>
       <c r="S3">
-        <v>301.1999999999998</v>
+        <v>3679.7</v>
       </c>
       <c r="T3">
-        <v>0.04654253264312753</v>
+        <v>0.4781314968814969</v>
       </c>
       <c r="U3">
-        <v>31761.9</v>
+        <v>25871.8</v>
       </c>
       <c r="V3">
-        <v>0.4463078524967717</v>
+        <v>0.389281436765352</v>
       </c>
       <c r="W3">
-        <v>0.08617886385081321</v>
+        <v>0.09539652028192616</v>
       </c>
       <c r="X3">
-        <v>0.06941631435079323</v>
+        <v>0.1090515518677914</v>
       </c>
       <c r="Y3">
-        <v>0.01676254950001997</v>
+        <v>-0.01365503158586526</v>
       </c>
       <c r="Z3">
-        <v>1.523118113697166</v>
+        <v>1.175668269155483</v>
       </c>
       <c r="AA3">
-        <v>0.07761575281635245</v>
+        <v>0.08835393365697664</v>
       </c>
       <c r="AB3">
-        <v>0.04682024093996177</v>
+        <v>0.07717571187450774</v>
       </c>
       <c r="AC3">
-        <v>0.03079551187639069</v>
+        <v>0.0111782217824689</v>
       </c>
       <c r="AD3">
-        <v>66299.5</v>
+        <v>61725.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>66299.5</v>
+        <v>61725.9</v>
       </c>
       <c r="AG3">
-        <v>34537.6</v>
+        <v>35854.10000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4822995459221012</v>
+        <v>0.4815327378978878</v>
       </c>
       <c r="AI3">
-        <v>0.4109792413625522</v>
+        <v>0.4874800983080403</v>
       </c>
       <c r="AJ3">
-        <v>0.3267403633749119</v>
+        <v>0.3504302909167323</v>
       </c>
       <c r="AK3">
-        <v>0.2665783670593066</v>
+        <v>0.3558698409736518</v>
       </c>
       <c r="AL3">
-        <v>578.6</v>
+        <v>381.6</v>
       </c>
       <c r="AM3">
-        <v>578.6</v>
+        <v>381.6</v>
       </c>
       <c r="AN3">
-        <v>6.325443165989276</v>
+        <v>5.346501979194636</v>
       </c>
       <c r="AO3">
-        <v>16.3814379536813</v>
+        <v>27.34224318658281</v>
       </c>
       <c r="AP3">
-        <v>3.295132329650619</v>
+        <v>3.105568596200986</v>
       </c>
       <c r="AQ3">
-        <v>16.3814379536813</v>
+        <v>27.34224318658281</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_general.xlsx
@@ -588,124 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0386</v>
+        <v>-0.0367</v>
       </c>
       <c r="E2">
-        <v>0.0469</v>
+        <v>0.0302</v>
       </c>
       <c r="F2">
-        <v>0.07820000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="G2">
-        <v>0.1070767345525261</v>
+        <v>0.09795910670848602</v>
       </c>
       <c r="H2">
-        <v>0.1070767345525261</v>
+        <v>0.09795910670848602</v>
       </c>
       <c r="I2">
-        <v>0.09264976845993668</v>
+        <v>0.08886133257428756</v>
       </c>
       <c r="J2">
-        <v>0.07515209517429933</v>
+        <v>0.06920649286478125</v>
       </c>
       <c r="K2">
-        <v>7742</v>
+        <v>7266.4</v>
       </c>
       <c r="L2">
-        <v>0.06874719732186067</v>
+        <v>0.06524680810179594</v>
       </c>
       <c r="M2">
-        <v>7696</v>
+        <v>7173.6</v>
       </c>
       <c r="N2">
-        <v>0.1157982798779424</v>
+        <v>0.1007175861250771</v>
       </c>
       <c r="O2">
-        <v>0.9940583828468096</v>
+        <v>0.9872288891335463</v>
       </c>
       <c r="P2">
-        <v>4016.3</v>
+        <v>4102.6</v>
       </c>
       <c r="Q2">
-        <v>0.06043147498359926</v>
+        <v>0.05760064247194451</v>
       </c>
       <c r="R2">
-        <v>0.5187677602686644</v>
+        <v>0.5645987008697567</v>
       </c>
       <c r="S2">
-        <v>3679.7</v>
+        <v>3071</v>
       </c>
       <c r="T2">
-        <v>0.4781314968814969</v>
+        <v>0.4280974684955949</v>
       </c>
       <c r="U2">
-        <v>25871.8</v>
+        <v>29234.7</v>
       </c>
       <c r="V2">
-        <v>0.389281436765352</v>
+        <v>0.4104561747366441</v>
       </c>
       <c r="W2">
-        <v>0.09539652028192616</v>
+        <v>0.1320359417445738</v>
       </c>
       <c r="X2">
-        <v>0.1090515518677914</v>
+        <v>0.09420718876291964</v>
       </c>
       <c r="Y2">
-        <v>-0.01365503158586526</v>
+        <v>0.03782875298165411</v>
       </c>
       <c r="Z2">
-        <v>1.175668269155483</v>
+        <v>1.54561288585537</v>
       </c>
       <c r="AA2">
-        <v>0.08835393365697664</v>
+        <v>0.1069664471566637</v>
       </c>
       <c r="AB2">
-        <v>0.07717571187450774</v>
+        <v>0.06860534738139505</v>
       </c>
       <c r="AC2">
-        <v>0.0111782217824689</v>
+        <v>0.03836109977526861</v>
       </c>
       <c r="AD2">
-        <v>61725.9</v>
+        <v>63867.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>61725.9</v>
+        <v>63867.9</v>
       </c>
       <c r="AG2">
-        <v>35854.10000000001</v>
+        <v>34633.2</v>
       </c>
       <c r="AH2">
-        <v>0.4815327378978878</v>
+        <v>0.4727705695640331</v>
       </c>
       <c r="AI2">
-        <v>0.4874800983080403</v>
+        <v>0.512231564831865</v>
       </c>
       <c r="AJ2">
-        <v>0.3504302909167323</v>
+        <v>0.3271662725856595</v>
       </c>
       <c r="AK2">
-        <v>0.3558698409736518</v>
+        <v>0.3628378569505369</v>
       </c>
       <c r="AL2">
-        <v>381.6</v>
+        <v>593.9</v>
       </c>
       <c r="AM2">
-        <v>381.6</v>
-      </c>
-      <c r="AN2">
-        <v>5.346501979194636</v>
+        <v>593.9</v>
       </c>
       <c r="AO2">
-        <v>27.34224318658281</v>
-      </c>
-      <c r="AP2">
-        <v>3.105568596200986</v>
+        <v>16.663242970197</v>
       </c>
       <c r="AQ2">
-        <v>27.34224318658281</v>
+        <v>16.663242970197</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0386</v>
+        <v>-0.0367</v>
       </c>
       <c r="E3">
-        <v>0.0469</v>
+        <v>0.0302</v>
       </c>
       <c r="F3">
-        <v>0.07820000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="G3">
-        <v>0.1070767345525261</v>
+        <v>0.09795910670848602</v>
       </c>
       <c r="H3">
-        <v>0.1070767345525261</v>
+        <v>0.09795910670848602</v>
       </c>
       <c r="I3">
-        <v>0.09264976845993668</v>
+        <v>0.08886133257428756</v>
       </c>
       <c r="J3">
-        <v>0.07515209517429933</v>
+        <v>0.06920649286478125</v>
       </c>
       <c r="K3">
-        <v>7742</v>
+        <v>7266.4</v>
       </c>
       <c r="L3">
-        <v>0.06874719732186067</v>
+        <v>0.06524680810179594</v>
       </c>
       <c r="M3">
-        <v>7696</v>
+        <v>7173.6</v>
       </c>
       <c r="N3">
-        <v>0.1157982798779424</v>
+        <v>0.1007175861250771</v>
       </c>
       <c r="O3">
-        <v>0.9940583828468096</v>
+        <v>0.9872288891335463</v>
       </c>
       <c r="P3">
-        <v>4016.3</v>
+        <v>4102.6</v>
       </c>
       <c r="Q3">
-        <v>0.06043147498359926</v>
+        <v>0.05760064247194451</v>
       </c>
       <c r="R3">
-        <v>0.5187677602686644</v>
+        <v>0.5645987008697567</v>
       </c>
       <c r="S3">
-        <v>3679.7</v>
+        <v>3071</v>
       </c>
       <c r="T3">
-        <v>0.4781314968814969</v>
+        <v>0.4280974684955949</v>
       </c>
       <c r="U3">
-        <v>25871.8</v>
+        <v>29234.7</v>
       </c>
       <c r="V3">
-        <v>0.389281436765352</v>
+        <v>0.4104561747366441</v>
       </c>
       <c r="W3">
-        <v>0.09539652028192616</v>
+        <v>0.1320359417445738</v>
       </c>
       <c r="X3">
-        <v>0.1090515518677914</v>
+        <v>0.09420718876291964</v>
       </c>
       <c r="Y3">
-        <v>-0.01365503158586526</v>
+        <v>0.03782875298165411</v>
       </c>
       <c r="Z3">
-        <v>1.175668269155483</v>
+        <v>1.54561288585537</v>
       </c>
       <c r="AA3">
-        <v>0.08835393365697664</v>
+        <v>0.1069664471566637</v>
       </c>
       <c r="AB3">
-        <v>0.07717571187450774</v>
+        <v>0.06860534738139505</v>
       </c>
       <c r="AC3">
-        <v>0.0111782217824689</v>
+        <v>0.03836109977526861</v>
       </c>
       <c r="AD3">
-        <v>61725.9</v>
+        <v>63867.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>61725.9</v>
+        <v>63867.9</v>
       </c>
       <c r="AG3">
-        <v>35854.10000000001</v>
+        <v>34633.2</v>
       </c>
       <c r="AH3">
-        <v>0.4815327378978878</v>
+        <v>0.4727705695640331</v>
       </c>
       <c r="AI3">
-        <v>0.4874800983080403</v>
+        <v>0.512231564831865</v>
       </c>
       <c r="AJ3">
-        <v>0.3504302909167323</v>
+        <v>0.3271662725856595</v>
       </c>
       <c r="AK3">
-        <v>0.3558698409736518</v>
+        <v>0.3628378569505369</v>
       </c>
       <c r="AL3">
-        <v>381.6</v>
+        <v>593.9</v>
       </c>
       <c r="AM3">
-        <v>381.6</v>
-      </c>
-      <c r="AN3">
-        <v>5.346501979194636</v>
+        <v>593.9</v>
       </c>
       <c r="AO3">
-        <v>27.34224318658281</v>
-      </c>
-      <c r="AP3">
-        <v>3.105568596200986</v>
+        <v>16.663242970197</v>
       </c>
       <c r="AQ3">
-        <v>27.34224318658281</v>
+        <v>16.663242970197</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_general.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0367</v>
+        <v>-0.061</v>
       </c>
       <c r="E2">
-        <v>0.0302</v>
+        <v>0.345</v>
       </c>
       <c r="F2">
-        <v>0.114</v>
+        <v>0.0832</v>
       </c>
       <c r="G2">
-        <v>0.09795910670848602</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.09795910670848602</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.08886133257428756</v>
+        <v>0.1099427174479891</v>
       </c>
       <c r="J2">
-        <v>0.06920649286478125</v>
+        <v>0.08775457395828838</v>
       </c>
       <c r="K2">
-        <v>7266.4</v>
+        <v>7903.1</v>
       </c>
       <c r="L2">
-        <v>0.06524680810179594</v>
+        <v>0.0814519137814111</v>
       </c>
       <c r="M2">
-        <v>7173.6</v>
+        <v>9261.799999999999</v>
       </c>
       <c r="N2">
-        <v>0.1007175861250771</v>
+        <v>0.1234134920962758</v>
       </c>
       <c r="O2">
-        <v>0.9872288891335463</v>
+        <v>1.17191987954094</v>
       </c>
       <c r="P2">
-        <v>4102.6</v>
+        <v>5043.4</v>
       </c>
       <c r="Q2">
-        <v>0.05760064247194451</v>
+        <v>0.06720330886419026</v>
       </c>
       <c r="R2">
-        <v>0.5645987008697567</v>
+        <v>0.6381546481760321</v>
       </c>
       <c r="S2">
-        <v>3071</v>
+        <v>4218.4</v>
       </c>
       <c r="T2">
-        <v>0.4280974684955949</v>
+        <v>0.4554622211665119</v>
       </c>
       <c r="U2">
-        <v>29234.7</v>
+        <v>23654.8</v>
       </c>
       <c r="V2">
-        <v>0.4104561747366441</v>
+        <v>0.3152002281240131</v>
       </c>
       <c r="W2">
-        <v>0.1320359417445738</v>
+        <v>0.1576763237121999</v>
       </c>
       <c r="X2">
-        <v>0.09420718876291964</v>
+        <v>0.09854336748124709</v>
       </c>
       <c r="Y2">
-        <v>0.03782875298165411</v>
+        <v>0.05913295623095285</v>
       </c>
       <c r="Z2">
-        <v>1.54561288585537</v>
+        <v>1.474409607357171</v>
       </c>
       <c r="AA2">
-        <v>0.1069664471566637</v>
+        <v>0.1293861869336358</v>
       </c>
       <c r="AB2">
-        <v>0.06860534738139505</v>
+        <v>0.07347107179406616</v>
       </c>
       <c r="AC2">
-        <v>0.03836109977526861</v>
+        <v>0.05591511513956963</v>
       </c>
       <c r="AD2">
-        <v>63867.9</v>
+        <v>65121.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>63867.9</v>
+        <v>65121.6</v>
       </c>
       <c r="AG2">
-        <v>34633.2</v>
+        <v>41466.8</v>
       </c>
       <c r="AH2">
-        <v>0.4727705695640331</v>
+        <v>0.4645951123112539</v>
       </c>
       <c r="AI2">
-        <v>0.512231564831865</v>
+        <v>0.5073541957363662</v>
       </c>
       <c r="AJ2">
-        <v>0.3271662725856595</v>
+        <v>0.3558963452366546</v>
       </c>
       <c r="AK2">
-        <v>0.3628378569505369</v>
+        <v>0.3960515947870354</v>
       </c>
       <c r="AL2">
-        <v>593.9</v>
+        <v>637.5</v>
       </c>
       <c r="AM2">
-        <v>593.9</v>
+        <v>637.5</v>
       </c>
       <c r="AO2">
-        <v>16.663242970197</v>
+        <v>16.73333333333333</v>
       </c>
       <c r="AQ2">
-        <v>16.663242970197</v>
+        <v>16.73333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0367</v>
+        <v>-0.061</v>
       </c>
       <c r="E3">
-        <v>0.0302</v>
+        <v>0.345</v>
       </c>
       <c r="F3">
-        <v>0.114</v>
+        <v>0.0832</v>
       </c>
       <c r="G3">
-        <v>0.09795910670848602</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.09795910670848602</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.08886133257428756</v>
+        <v>0.1099427174479891</v>
       </c>
       <c r="J3">
-        <v>0.06920649286478125</v>
+        <v>0.08775457395828838</v>
       </c>
       <c r="K3">
-        <v>7266.4</v>
+        <v>7903.1</v>
       </c>
       <c r="L3">
-        <v>0.06524680810179594</v>
+        <v>0.0814519137814111</v>
       </c>
       <c r="M3">
-        <v>7173.6</v>
+        <v>9261.799999999999</v>
       </c>
       <c r="N3">
-        <v>0.1007175861250771</v>
+        <v>0.1234134920962758</v>
       </c>
       <c r="O3">
-        <v>0.9872288891335463</v>
+        <v>1.17191987954094</v>
       </c>
       <c r="P3">
-        <v>4102.6</v>
+        <v>5043.4</v>
       </c>
       <c r="Q3">
-        <v>0.05760064247194451</v>
+        <v>0.06720330886419026</v>
       </c>
       <c r="R3">
-        <v>0.5645987008697567</v>
+        <v>0.6381546481760321</v>
       </c>
       <c r="S3">
-        <v>3071</v>
+        <v>4218.4</v>
       </c>
       <c r="T3">
-        <v>0.4280974684955949</v>
+        <v>0.4554622211665119</v>
       </c>
       <c r="U3">
-        <v>29234.7</v>
+        <v>23654.8</v>
       </c>
       <c r="V3">
-        <v>0.4104561747366441</v>
+        <v>0.3152002281240131</v>
       </c>
       <c r="W3">
-        <v>0.1320359417445738</v>
+        <v>0.1576763237121999</v>
       </c>
       <c r="X3">
-        <v>0.09420718876291964</v>
+        <v>0.09854336748124709</v>
       </c>
       <c r="Y3">
-        <v>0.03782875298165411</v>
+        <v>0.05913295623095285</v>
       </c>
       <c r="Z3">
-        <v>1.54561288585537</v>
+        <v>1.474409607357171</v>
       </c>
       <c r="AA3">
-        <v>0.1069664471566637</v>
+        <v>0.1293861869336358</v>
       </c>
       <c r="AB3">
-        <v>0.06860534738139505</v>
+        <v>0.07347107179406616</v>
       </c>
       <c r="AC3">
-        <v>0.03836109977526861</v>
+        <v>0.05591511513956963</v>
       </c>
       <c r="AD3">
-        <v>63867.9</v>
+        <v>65121.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>63867.9</v>
+        <v>65121.6</v>
       </c>
       <c r="AG3">
-        <v>34633.2</v>
+        <v>41466.8</v>
       </c>
       <c r="AH3">
-        <v>0.4727705695640331</v>
+        <v>0.4645951123112539</v>
       </c>
       <c r="AI3">
-        <v>0.512231564831865</v>
+        <v>0.5073541957363662</v>
       </c>
       <c r="AJ3">
-        <v>0.3271662725856595</v>
+        <v>0.3558963452366546</v>
       </c>
       <c r="AK3">
-        <v>0.3628378569505369</v>
+        <v>0.3960515947870354</v>
       </c>
       <c r="AL3">
-        <v>593.9</v>
+        <v>637.5</v>
       </c>
       <c r="AM3">
-        <v>593.9</v>
+        <v>637.5</v>
       </c>
       <c r="AO3">
-        <v>16.663242970197</v>
+        <v>16.73333333333333</v>
       </c>
       <c r="AQ3">
-        <v>16.663242970197</v>
+        <v>16.73333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_general.xlsx
@@ -648,10 +648,10 @@
         <v>0.1576763237121999</v>
       </c>
       <c r="X2">
-        <v>0.09854336748124709</v>
+        <v>0.09851873580863946</v>
       </c>
       <c r="Y2">
-        <v>0.05913295623095285</v>
+        <v>0.05915758790356049</v>
       </c>
       <c r="Z2">
         <v>1.474409607357171</v>
@@ -660,10 +660,10 @@
         <v>0.1293861869336358</v>
       </c>
       <c r="AB2">
-        <v>0.07347107179406616</v>
+        <v>0.07345788387616009</v>
       </c>
       <c r="AC2">
-        <v>0.05591511513956963</v>
+        <v>0.0559283030574757</v>
       </c>
       <c r="AD2">
         <v>65121.6</v>
@@ -779,10 +779,10 @@
         <v>0.1576763237121999</v>
       </c>
       <c r="X3">
-        <v>0.09854336748124709</v>
+        <v>0.09851873580863946</v>
       </c>
       <c r="Y3">
-        <v>0.05913295623095285</v>
+        <v>0.05915758790356049</v>
       </c>
       <c r="Z3">
         <v>1.474409607357171</v>
@@ -791,10 +791,10 @@
         <v>0.1293861869336358</v>
       </c>
       <c r="AB3">
-        <v>0.07347107179406616</v>
+        <v>0.07345788387616009</v>
       </c>
       <c r="AC3">
-        <v>0.05591511513956963</v>
+        <v>0.0559283030574757</v>
       </c>
       <c r="AD3">
         <v>65121.6</v>
